--- a/KatalonData/RADTestData/CRNNotZero.xlsx
+++ b/KatalonData/RADTestData/CRNNotZero.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="75">
   <si>
     <t>Result</t>
   </si>
@@ -213,6 +213,57 @@
   </si>
   <si>
     <t>Thu Jul 09 22:25:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:07:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:07:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:08:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:09:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:09:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:10:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:10:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:11:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:11:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:12:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:12:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:13:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:13:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:14:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:14:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:15:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:15:44 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -626,7 +677,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -646,7 +697,7 @@
         <v>20</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -666,7 +717,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -686,7 +737,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -706,7 +757,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
@@ -726,7 +777,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
@@ -746,7 +797,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>11</v>
@@ -766,7 +817,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -786,7 +837,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
@@ -806,7 +857,7 @@
         <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -826,7 +877,7 @@
         <v>20</v>
       </c>
       <c r="B12" t="s" s="1">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -846,7 +897,7 @@
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>11</v>
@@ -866,7 +917,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>11</v>
@@ -886,7 +937,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>11</v>
@@ -906,7 +957,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>11</v>
@@ -926,7 +977,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>11</v>
@@ -946,7 +997,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>11</v>

--- a/KatalonData/RADTestData/CRNNotZero.xlsx
+++ b/KatalonData/RADTestData/CRNNotZero.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="75">
   <si>
     <t>Result</t>
   </si>
@@ -213,6 +213,57 @@
   </si>
   <si>
     <t>Thu Jul 09 22:25:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:30:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:30:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:30:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:30:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:30:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:31:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:31:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:31:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:31:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:31:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:32:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:32:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:32:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:32:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:32:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:33:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:33:21 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -626,7 +677,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -646,7 +697,7 @@
         <v>20</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -666,7 +717,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -686,7 +737,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -706,7 +757,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
@@ -726,7 +777,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
@@ -746,7 +797,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>11</v>
@@ -766,7 +817,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -786,7 +837,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
@@ -806,7 +857,7 @@
         <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -826,7 +877,7 @@
         <v>20</v>
       </c>
       <c r="B12" t="s" s="1">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -846,7 +897,7 @@
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>11</v>
@@ -866,7 +917,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>11</v>
@@ -886,7 +937,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>11</v>
@@ -906,7 +957,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>11</v>
@@ -926,7 +977,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>11</v>
@@ -946,7 +997,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>11</v>
